--- a/projects/ecm-compute/v1.0.0/export/角色管理/角色管理_params.xlsx
+++ b/projects/ecm-compute/v1.0.0/export/角色管理/角色管理_params.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>e_tenantId</t>
+          <t>e_name_policyName</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,19 +617,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>${tenantId}</t>
+          <t>${gen_test_name('policyName')}</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.tenantId)</t>
+          <t>步骤 创建角色 的名称字段</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>e_adminId</t>
+          <t>e_mutable_description</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -639,54 +639,10 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>${adminId}</t>
+          <t>${gen_mutable_value()}</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>由 获取当前用户信息 提取 (path: entity.id)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>e_name_policyName</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>${gen_test_name('policyName')}</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>步骤 创建角色 的名称字段</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>e_mutable_description</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>${gen_mutable_value()}</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>步骤 创建角色 的可变字段</t>
         </is>
